--- a/docs/ops/tresor-catalogue-TEMPLATE.xlsx
+++ b/docs/ops/tresor-catalogue-TEMPLATE.xlsx
@@ -9,10 +9,17 @@
   <sheets>
     <sheet name="Catalogue" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stock Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="How To Use" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Orders &amp; Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Action Tracker" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="How To Use" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Lists" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catalogue'!$A$1:$AC$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock Log'!$A$1:$G$600</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Orders &amp; Returns'!$A$1:$N$400</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action Tracker'!$A$1:$G$120</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -88,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -103,6 +110,13 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -114,7 +128,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -126,6 +140,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FBEAC9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D8EFDD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4556,6 +4577,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC200"/>
   <conditionalFormatting sqref="S2:S200">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$S2="OUT OF STOCK"</formula>
@@ -4608,15 +4630,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4632,20 +4655,25 @@
       </c>
       <c r="C1" s="11" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>What Happened</t>
         </is>
       </c>
       <c r="D1" s="11" t="inlineStr">
         <is>
-          <t>Qty (+in / −out)</t>
+          <t>Qty  (+ in / − out)</t>
         </is>
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>Reference (PO / Order)</t>
+          <t>Stock After</t>
         </is>
       </c>
       <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Reference (PO / Order no.)</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -4664,27 +4692,3620 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Received (new stock)</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="2">
+        <f>IF($B2="","",SUMIFS($D$2:$D2,$B$2:$B2,$B2))</f>
+        <v/>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>PO-001</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>EXAMPLE ROW — first stock intake</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="E3" s="10">
+        <f>IF($B3="","",SUMIFS($D$2:$D3,$B$2:$B3,$B3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="E4" s="10">
+        <f>IF($B4="","",SUMIFS($D$2:$D4,$B$2:$B4,$B4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" s="10">
+        <f>IF($B5="","",SUMIFS($D$2:$D5,$B$2:$B5,$B5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" s="10">
+        <f>IF($B6="","",SUMIFS($D$2:$D6,$B$2:$B6,$B6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="E7" s="10">
+        <f>IF($B7="","",SUMIFS($D$2:$D7,$B$2:$B7,$B7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="E8" s="10">
+        <f>IF($B8="","",SUMIFS($D$2:$D8,$B$2:$B8,$B8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="E9" s="10">
+        <f>IF($B9="","",SUMIFS($D$2:$D9,$B$2:$B9,$B9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="E10" s="10">
+        <f>IF($B10="","",SUMIFS($D$2:$D10,$B$2:$B10,$B10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="E11" s="10">
+        <f>IF($B11="","",SUMIFS($D$2:$D11,$B$2:$B11,$B11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="E12" s="10">
+        <f>IF($B12="","",SUMIFS($D$2:$D12,$B$2:$B12,$B12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="E13" s="10">
+        <f>IF($B13="","",SUMIFS($D$2:$D13,$B$2:$B13,$B13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="E14" s="10">
+        <f>IF($B14="","",SUMIFS($D$2:$D14,$B$2:$B14,$B14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" s="10">
+        <f>IF($B15="","",SUMIFS($D$2:$D15,$B$2:$B15,$B15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="10">
+        <f>IF($B16="","",SUMIFS($D$2:$D16,$B$2:$B16,$B16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" s="10">
+        <f>IF($B17="","",SUMIFS($D$2:$D17,$B$2:$B17,$B17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" s="10">
+        <f>IF($B18="","",SUMIFS($D$2:$D18,$B$2:$B18,$B18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" s="10">
+        <f>IF($B19="","",SUMIFS($D$2:$D19,$B$2:$B19,$B19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" s="10">
+        <f>IF($B20="","",SUMIFS($D$2:$D20,$B$2:$B20,$B20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" s="10">
+        <f>IF($B21="","",SUMIFS($D$2:$D21,$B$2:$B21,$B21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" s="10">
+        <f>IF($B22="","",SUMIFS($D$2:$D22,$B$2:$B22,$B22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" s="10">
+        <f>IF($B23="","",SUMIFS($D$2:$D23,$B$2:$B23,$B23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" s="10">
+        <f>IF($B24="","",SUMIFS($D$2:$D24,$B$2:$B24,$B24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" s="10">
+        <f>IF($B25="","",SUMIFS($D$2:$D25,$B$2:$B25,$B25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" s="10">
+        <f>IF($B26="","",SUMIFS($D$2:$D26,$B$2:$B26,$B26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" s="10">
+        <f>IF($B27="","",SUMIFS($D$2:$D27,$B$2:$B27,$B27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" s="10">
+        <f>IF($B28="","",SUMIFS($D$2:$D28,$B$2:$B28,$B28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" s="10">
+        <f>IF($B29="","",SUMIFS($D$2:$D29,$B$2:$B29,$B29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" s="10">
+        <f>IF($B30="","",SUMIFS($D$2:$D30,$B$2:$B30,$B30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" s="10">
+        <f>IF($B31="","",SUMIFS($D$2:$D31,$B$2:$B31,$B31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" s="10">
+        <f>IF($B32="","",SUMIFS($D$2:$D32,$B$2:$B32,$B32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" s="10">
+        <f>IF($B33="","",SUMIFS($D$2:$D33,$B$2:$B33,$B33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" s="10">
+        <f>IF($B34="","",SUMIFS($D$2:$D34,$B$2:$B34,$B34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" s="10">
+        <f>IF($B35="","",SUMIFS($D$2:$D35,$B$2:$B35,$B35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="10">
+        <f>IF($B36="","",SUMIFS($D$2:$D36,$B$2:$B36,$B36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" s="10">
+        <f>IF($B37="","",SUMIFS($D$2:$D37,$B$2:$B37,$B37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" s="10">
+        <f>IF($B38="","",SUMIFS($D$2:$D38,$B$2:$B38,$B38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" s="10">
+        <f>IF($B39="","",SUMIFS($D$2:$D39,$B$2:$B39,$B39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" s="10">
+        <f>IF($B40="","",SUMIFS($D$2:$D40,$B$2:$B40,$B40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" s="10">
+        <f>IF($B41="","",SUMIFS($D$2:$D41,$B$2:$B41,$B41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" s="10">
+        <f>IF($B42="","",SUMIFS($D$2:$D42,$B$2:$B42,$B42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" s="10">
+        <f>IF($B43="","",SUMIFS($D$2:$D43,$B$2:$B43,$B43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="E44" s="10">
+        <f>IF($B44="","",SUMIFS($D$2:$D44,$B$2:$B44,$B44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="E45" s="10">
+        <f>IF($B45="","",SUMIFS($D$2:$D45,$B$2:$B45,$B45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="E46" s="10">
+        <f>IF($B46="","",SUMIFS($D$2:$D46,$B$2:$B46,$B46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="E47" s="10">
+        <f>IF($B47="","",SUMIFS($D$2:$D47,$B$2:$B47,$B47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="E48" s="10">
+        <f>IF($B48="","",SUMIFS($D$2:$D48,$B$2:$B48,$B48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="E49" s="10">
+        <f>IF($B49="","",SUMIFS($D$2:$D49,$B$2:$B49,$B49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="E50" s="10">
+        <f>IF($B50="","",SUMIFS($D$2:$D50,$B$2:$B50,$B50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="E51" s="10">
+        <f>IF($B51="","",SUMIFS($D$2:$D51,$B$2:$B51,$B51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" s="10">
+        <f>IF($B52="","",SUMIFS($D$2:$D52,$B$2:$B52,$B52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="E53" s="10">
+        <f>IF($B53="","",SUMIFS($D$2:$D53,$B$2:$B53,$B53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="E54" s="10">
+        <f>IF($B54="","",SUMIFS($D$2:$D54,$B$2:$B54,$B54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="E55" s="10">
+        <f>IF($B55="","",SUMIFS($D$2:$D55,$B$2:$B55,$B55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="E56" s="10">
+        <f>IF($B56="","",SUMIFS($D$2:$D56,$B$2:$B56,$B56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="E57" s="10">
+        <f>IF($B57="","",SUMIFS($D$2:$D57,$B$2:$B57,$B57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="E58" s="10">
+        <f>IF($B58="","",SUMIFS($D$2:$D58,$B$2:$B58,$B58))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="E59" s="10">
+        <f>IF($B59="","",SUMIFS($D$2:$D59,$B$2:$B59,$B59))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="E60" s="10">
+        <f>IF($B60="","",SUMIFS($D$2:$D60,$B$2:$B60,$B60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="E61" s="10">
+        <f>IF($B61="","",SUMIFS($D$2:$D61,$B$2:$B61,$B61))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="E62" s="10">
+        <f>IF($B62="","",SUMIFS($D$2:$D62,$B$2:$B62,$B62))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="E63" s="10">
+        <f>IF($B63="","",SUMIFS($D$2:$D63,$B$2:$B63,$B63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="E64" s="10">
+        <f>IF($B64="","",SUMIFS($D$2:$D64,$B$2:$B64,$B64))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="E65" s="10">
+        <f>IF($B65="","",SUMIFS($D$2:$D65,$B$2:$B65,$B65))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="E66" s="10">
+        <f>IF($B66="","",SUMIFS($D$2:$D66,$B$2:$B66,$B66))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="E67" s="10">
+        <f>IF($B67="","",SUMIFS($D$2:$D67,$B$2:$B67,$B67))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="E68" s="10">
+        <f>IF($B68="","",SUMIFS($D$2:$D68,$B$2:$B68,$B68))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="E69" s="10">
+        <f>IF($B69="","",SUMIFS($D$2:$D69,$B$2:$B69,$B69))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="E70" s="10">
+        <f>IF($B70="","",SUMIFS($D$2:$D70,$B$2:$B70,$B70))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="E71" s="10">
+        <f>IF($B71="","",SUMIFS($D$2:$D71,$B$2:$B71,$B71))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="E72" s="10">
+        <f>IF($B72="","",SUMIFS($D$2:$D72,$B$2:$B72,$B72))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="E73" s="10">
+        <f>IF($B73="","",SUMIFS($D$2:$D73,$B$2:$B73,$B73))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="E74" s="10">
+        <f>IF($B74="","",SUMIFS($D$2:$D74,$B$2:$B74,$B74))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="E75" s="10">
+        <f>IF($B75="","",SUMIFS($D$2:$D75,$B$2:$B75,$B75))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="E76" s="10">
+        <f>IF($B76="","",SUMIFS($D$2:$D76,$B$2:$B76,$B76))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" s="10">
+        <f>IF($B77="","",SUMIFS($D$2:$D77,$B$2:$B77,$B77))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="E78" s="10">
+        <f>IF($B78="","",SUMIFS($D$2:$D78,$B$2:$B78,$B78))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="E79" s="10">
+        <f>IF($B79="","",SUMIFS($D$2:$D79,$B$2:$B79,$B79))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="E80" s="10">
+        <f>IF($B80="","",SUMIFS($D$2:$D80,$B$2:$B80,$B80))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="E81" s="10">
+        <f>IF($B81="","",SUMIFS($D$2:$D81,$B$2:$B81,$B81))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="E82" s="10">
+        <f>IF($B82="","",SUMIFS($D$2:$D82,$B$2:$B82,$B82))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="E83" s="10">
+        <f>IF($B83="","",SUMIFS($D$2:$D83,$B$2:$B83,$B83))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="E84" s="10">
+        <f>IF($B84="","",SUMIFS($D$2:$D84,$B$2:$B84,$B84))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="E85" s="10">
+        <f>IF($B85="","",SUMIFS($D$2:$D85,$B$2:$B85,$B85))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="E86" s="10">
+        <f>IF($B86="","",SUMIFS($D$2:$D86,$B$2:$B86,$B86))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="E87" s="10">
+        <f>IF($B87="","",SUMIFS($D$2:$D87,$B$2:$B87,$B87))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="E88" s="10">
+        <f>IF($B88="","",SUMIFS($D$2:$D88,$B$2:$B88,$B88))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="E89" s="10">
+        <f>IF($B89="","",SUMIFS($D$2:$D89,$B$2:$B89,$B89))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="E90" s="10">
+        <f>IF($B90="","",SUMIFS($D$2:$D90,$B$2:$B90,$B90))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="E91" s="10">
+        <f>IF($B91="","",SUMIFS($D$2:$D91,$B$2:$B91,$B91))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="E92" s="10">
+        <f>IF($B92="","",SUMIFS($D$2:$D92,$B$2:$B92,$B92))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="E93" s="10">
+        <f>IF($B93="","",SUMIFS($D$2:$D93,$B$2:$B93,$B93))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="E94" s="10">
+        <f>IF($B94="","",SUMIFS($D$2:$D94,$B$2:$B94,$B94))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="E95" s="10">
+        <f>IF($B95="","",SUMIFS($D$2:$D95,$B$2:$B95,$B95))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="E96" s="10">
+        <f>IF($B96="","",SUMIFS($D$2:$D96,$B$2:$B96,$B96))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="E97" s="10">
+        <f>IF($B97="","",SUMIFS($D$2:$D97,$B$2:$B97,$B97))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="E98" s="10">
+        <f>IF($B98="","",SUMIFS($D$2:$D98,$B$2:$B98,$B98))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="E99" s="10">
+        <f>IF($B99="","",SUMIFS($D$2:$D99,$B$2:$B99,$B99))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="E100" s="10">
+        <f>IF($B100="","",SUMIFS($D$2:$D100,$B$2:$B100,$B100))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="E101" s="10">
+        <f>IF($B101="","",SUMIFS($D$2:$D101,$B$2:$B101,$B101))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="E102" s="10">
+        <f>IF($B102="","",SUMIFS($D$2:$D102,$B$2:$B102,$B102))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="E103" s="10">
+        <f>IF($B103="","",SUMIFS($D$2:$D103,$B$2:$B103,$B103))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="E104" s="10">
+        <f>IF($B104="","",SUMIFS($D$2:$D104,$B$2:$B104,$B104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="E105" s="10">
+        <f>IF($B105="","",SUMIFS($D$2:$D105,$B$2:$B105,$B105))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="E106" s="10">
+        <f>IF($B106="","",SUMIFS($D$2:$D106,$B$2:$B106,$B106))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="E107" s="10">
+        <f>IF($B107="","",SUMIFS($D$2:$D107,$B$2:$B107,$B107))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="E108" s="10">
+        <f>IF($B108="","",SUMIFS($D$2:$D108,$B$2:$B108,$B108))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="E109" s="10">
+        <f>IF($B109="","",SUMIFS($D$2:$D109,$B$2:$B109,$B109))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="E110" s="10">
+        <f>IF($B110="","",SUMIFS($D$2:$D110,$B$2:$B110,$B110))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="E111" s="10">
+        <f>IF($B111="","",SUMIFS($D$2:$D111,$B$2:$B111,$B111))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="E112" s="10">
+        <f>IF($B112="","",SUMIFS($D$2:$D112,$B$2:$B112,$B112))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="E113" s="10">
+        <f>IF($B113="","",SUMIFS($D$2:$D113,$B$2:$B113,$B113))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="E114" s="10">
+        <f>IF($B114="","",SUMIFS($D$2:$D114,$B$2:$B114,$B114))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="E115" s="10">
+        <f>IF($B115="","",SUMIFS($D$2:$D115,$B$2:$B115,$B115))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="E116" s="10">
+        <f>IF($B116="","",SUMIFS($D$2:$D116,$B$2:$B116,$B116))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="E117" s="10">
+        <f>IF($B117="","",SUMIFS($D$2:$D117,$B$2:$B117,$B117))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="E118" s="10">
+        <f>IF($B118="","",SUMIFS($D$2:$D118,$B$2:$B118,$B118))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="E119" s="10">
+        <f>IF($B119="","",SUMIFS($D$2:$D119,$B$2:$B119,$B119))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="E120" s="10">
+        <f>IF($B120="","",SUMIFS($D$2:$D120,$B$2:$B120,$B120))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="E121" s="10">
+        <f>IF($B121="","",SUMIFS($D$2:$D121,$B$2:$B121,$B121))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="E122" s="10">
+        <f>IF($B122="","",SUMIFS($D$2:$D122,$B$2:$B122,$B122))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="E123" s="10">
+        <f>IF($B123="","",SUMIFS($D$2:$D123,$B$2:$B123,$B123))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="E124" s="10">
+        <f>IF($B124="","",SUMIFS($D$2:$D124,$B$2:$B124,$B124))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="E125" s="10">
+        <f>IF($B125="","",SUMIFS($D$2:$D125,$B$2:$B125,$B125))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="E126" s="10">
+        <f>IF($B126="","",SUMIFS($D$2:$D126,$B$2:$B126,$B126))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="E127" s="10">
+        <f>IF($B127="","",SUMIFS($D$2:$D127,$B$2:$B127,$B127))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="E128" s="10">
+        <f>IF($B128="","",SUMIFS($D$2:$D128,$B$2:$B128,$B128))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="E129" s="10">
+        <f>IF($B129="","",SUMIFS($D$2:$D129,$B$2:$B129,$B129))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="E130" s="10">
+        <f>IF($B130="","",SUMIFS($D$2:$D130,$B$2:$B130,$B130))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="E131" s="10">
+        <f>IF($B131="","",SUMIFS($D$2:$D131,$B$2:$B131,$B131))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="E132" s="10">
+        <f>IF($B132="","",SUMIFS($D$2:$D132,$B$2:$B132,$B132))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="E133" s="10">
+        <f>IF($B133="","",SUMIFS($D$2:$D133,$B$2:$B133,$B133))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="E134" s="10">
+        <f>IF($B134="","",SUMIFS($D$2:$D134,$B$2:$B134,$B134))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="E135" s="10">
+        <f>IF($B135="","",SUMIFS($D$2:$D135,$B$2:$B135,$B135))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="E136" s="10">
+        <f>IF($B136="","",SUMIFS($D$2:$D136,$B$2:$B136,$B136))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="E137" s="10">
+        <f>IF($B137="","",SUMIFS($D$2:$D137,$B$2:$B137,$B137))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="E138" s="10">
+        <f>IF($B138="","",SUMIFS($D$2:$D138,$B$2:$B138,$B138))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="E139" s="10">
+        <f>IF($B139="","",SUMIFS($D$2:$D139,$B$2:$B139,$B139))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="E140" s="10">
+        <f>IF($B140="","",SUMIFS($D$2:$D140,$B$2:$B140,$B140))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="E141" s="10">
+        <f>IF($B141="","",SUMIFS($D$2:$D141,$B$2:$B141,$B141))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="E142" s="10">
+        <f>IF($B142="","",SUMIFS($D$2:$D142,$B$2:$B142,$B142))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="E143" s="10">
+        <f>IF($B143="","",SUMIFS($D$2:$D143,$B$2:$B143,$B143))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="E144" s="10">
+        <f>IF($B144="","",SUMIFS($D$2:$D144,$B$2:$B144,$B144))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="E145" s="10">
+        <f>IF($B145="","",SUMIFS($D$2:$D145,$B$2:$B145,$B145))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="E146" s="10">
+        <f>IF($B146="","",SUMIFS($D$2:$D146,$B$2:$B146,$B146))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="E147" s="10">
+        <f>IF($B147="","",SUMIFS($D$2:$D147,$B$2:$B147,$B147))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="E148" s="10">
+        <f>IF($B148="","",SUMIFS($D$2:$D148,$B$2:$B148,$B148))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="E149" s="10">
+        <f>IF($B149="","",SUMIFS($D$2:$D149,$B$2:$B149,$B149))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="E150" s="10">
+        <f>IF($B150="","",SUMIFS($D$2:$D150,$B$2:$B150,$B150))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="E151" s="10">
+        <f>IF($B151="","",SUMIFS($D$2:$D151,$B$2:$B151,$B151))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="E152" s="10">
+        <f>IF($B152="","",SUMIFS($D$2:$D152,$B$2:$B152,$B152))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="E153" s="10">
+        <f>IF($B153="","",SUMIFS($D$2:$D153,$B$2:$B153,$B153))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="E154" s="10">
+        <f>IF($B154="","",SUMIFS($D$2:$D154,$B$2:$B154,$B154))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="E155" s="10">
+        <f>IF($B155="","",SUMIFS($D$2:$D155,$B$2:$B155,$B155))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="E156" s="10">
+        <f>IF($B156="","",SUMIFS($D$2:$D156,$B$2:$B156,$B156))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="E157" s="10">
+        <f>IF($B157="","",SUMIFS($D$2:$D157,$B$2:$B157,$B157))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="E158" s="10">
+        <f>IF($B158="","",SUMIFS($D$2:$D158,$B$2:$B158,$B158))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="E159" s="10">
+        <f>IF($B159="","",SUMIFS($D$2:$D159,$B$2:$B159,$B159))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="E160" s="10">
+        <f>IF($B160="","",SUMIFS($D$2:$D160,$B$2:$B160,$B160))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="E161" s="10">
+        <f>IF($B161="","",SUMIFS($D$2:$D161,$B$2:$B161,$B161))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="E162" s="10">
+        <f>IF($B162="","",SUMIFS($D$2:$D162,$B$2:$B162,$B162))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="E163" s="10">
+        <f>IF($B163="","",SUMIFS($D$2:$D163,$B$2:$B163,$B163))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="E164" s="10">
+        <f>IF($B164="","",SUMIFS($D$2:$D164,$B$2:$B164,$B164))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="E165" s="10">
+        <f>IF($B165="","",SUMIFS($D$2:$D165,$B$2:$B165,$B165))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="E166" s="10">
+        <f>IF($B166="","",SUMIFS($D$2:$D166,$B$2:$B166,$B166))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="E167" s="10">
+        <f>IF($B167="","",SUMIFS($D$2:$D167,$B$2:$B167,$B167))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="E168" s="10">
+        <f>IF($B168="","",SUMIFS($D$2:$D168,$B$2:$B168,$B168))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="E169" s="10">
+        <f>IF($B169="","",SUMIFS($D$2:$D169,$B$2:$B169,$B169))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="E170" s="10">
+        <f>IF($B170="","",SUMIFS($D$2:$D170,$B$2:$B170,$B170))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="E171" s="10">
+        <f>IF($B171="","",SUMIFS($D$2:$D171,$B$2:$B171,$B171))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="E172" s="10">
+        <f>IF($B172="","",SUMIFS($D$2:$D172,$B$2:$B172,$B172))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="E173" s="10">
+        <f>IF($B173="","",SUMIFS($D$2:$D173,$B$2:$B173,$B173))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="E174" s="10">
+        <f>IF($B174="","",SUMIFS($D$2:$D174,$B$2:$B174,$B174))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="E175" s="10">
+        <f>IF($B175="","",SUMIFS($D$2:$D175,$B$2:$B175,$B175))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="E176" s="10">
+        <f>IF($B176="","",SUMIFS($D$2:$D176,$B$2:$B176,$B176))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="E177" s="10">
+        <f>IF($B177="","",SUMIFS($D$2:$D177,$B$2:$B177,$B177))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="E178" s="10">
+        <f>IF($B178="","",SUMIFS($D$2:$D178,$B$2:$B178,$B178))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="E179" s="10">
+        <f>IF($B179="","",SUMIFS($D$2:$D179,$B$2:$B179,$B179))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="E180" s="10">
+        <f>IF($B180="","",SUMIFS($D$2:$D180,$B$2:$B180,$B180))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="E181" s="10">
+        <f>IF($B181="","",SUMIFS($D$2:$D181,$B$2:$B181,$B181))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="E182" s="10">
+        <f>IF($B182="","",SUMIFS($D$2:$D182,$B$2:$B182,$B182))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="E183" s="10">
+        <f>IF($B183="","",SUMIFS($D$2:$D183,$B$2:$B183,$B183))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="E184" s="10">
+        <f>IF($B184="","",SUMIFS($D$2:$D184,$B$2:$B184,$B184))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="E185" s="10">
+        <f>IF($B185="","",SUMIFS($D$2:$D185,$B$2:$B185,$B185))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="E186" s="10">
+        <f>IF($B186="","",SUMIFS($D$2:$D186,$B$2:$B186,$B186))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="E187" s="10">
+        <f>IF($B187="","",SUMIFS($D$2:$D187,$B$2:$B187,$B187))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="E188" s="10">
+        <f>IF($B188="","",SUMIFS($D$2:$D188,$B$2:$B188,$B188))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="E189" s="10">
+        <f>IF($B189="","",SUMIFS($D$2:$D189,$B$2:$B189,$B189))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="E190" s="10">
+        <f>IF($B190="","",SUMIFS($D$2:$D190,$B$2:$B190,$B190))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="E191" s="10">
+        <f>IF($B191="","",SUMIFS($D$2:$D191,$B$2:$B191,$B191))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="E192" s="10">
+        <f>IF($B192="","",SUMIFS($D$2:$D192,$B$2:$B192,$B192))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="E193" s="10">
+        <f>IF($B193="","",SUMIFS($D$2:$D193,$B$2:$B193,$B193))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="E194" s="10">
+        <f>IF($B194="","",SUMIFS($D$2:$D194,$B$2:$B194,$B194))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="E195" s="10">
+        <f>IF($B195="","",SUMIFS($D$2:$D195,$B$2:$B195,$B195))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="E196" s="10">
+        <f>IF($B196="","",SUMIFS($D$2:$D196,$B$2:$B196,$B196))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="E197" s="10">
+        <f>IF($B197="","",SUMIFS($D$2:$D197,$B$2:$B197,$B197))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="E198" s="10">
+        <f>IF($B198="","",SUMIFS($D$2:$D198,$B$2:$B198,$B198))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="E199" s="10">
+        <f>IF($B199="","",SUMIFS($D$2:$D199,$B$2:$B199,$B199))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="E200" s="10">
+        <f>IF($B200="","",SUMIFS($D$2:$D200,$B$2:$B200,$B200))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="E201" s="10">
+        <f>IF($B201="","",SUMIFS($D$2:$D201,$B$2:$B201,$B201))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="E202" s="10">
+        <f>IF($B202="","",SUMIFS($D$2:$D202,$B$2:$B202,$B202))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="E203" s="10">
+        <f>IF($B203="","",SUMIFS($D$2:$D203,$B$2:$B203,$B203))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="E204" s="10">
+        <f>IF($B204="","",SUMIFS($D$2:$D204,$B$2:$B204,$B204))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="E205" s="10">
+        <f>IF($B205="","",SUMIFS($D$2:$D205,$B$2:$B205,$B205))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="E206" s="10">
+        <f>IF($B206="","",SUMIFS($D$2:$D206,$B$2:$B206,$B206))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="E207" s="10">
+        <f>IF($B207="","",SUMIFS($D$2:$D207,$B$2:$B207,$B207))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="E208" s="10">
+        <f>IF($B208="","",SUMIFS($D$2:$D208,$B$2:$B208,$B208))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="E209" s="10">
+        <f>IF($B209="","",SUMIFS($D$2:$D209,$B$2:$B209,$B209))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="E210" s="10">
+        <f>IF($B210="","",SUMIFS($D$2:$D210,$B$2:$B210,$B210))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="E211" s="10">
+        <f>IF($B211="","",SUMIFS($D$2:$D211,$B$2:$B211,$B211))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="E212" s="10">
+        <f>IF($B212="","",SUMIFS($D$2:$D212,$B$2:$B212,$B212))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="E213" s="10">
+        <f>IF($B213="","",SUMIFS($D$2:$D213,$B$2:$B213,$B213))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="E214" s="10">
+        <f>IF($B214="","",SUMIFS($D$2:$D214,$B$2:$B214,$B214))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="E215" s="10">
+        <f>IF($B215="","",SUMIFS($D$2:$D215,$B$2:$B215,$B215))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="E216" s="10">
+        <f>IF($B216="","",SUMIFS($D$2:$D216,$B$2:$B216,$B216))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="E217" s="10">
+        <f>IF($B217="","",SUMIFS($D$2:$D217,$B$2:$B217,$B217))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="E218" s="10">
+        <f>IF($B218="","",SUMIFS($D$2:$D218,$B$2:$B218,$B218))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="E219" s="10">
+        <f>IF($B219="","",SUMIFS($D$2:$D219,$B$2:$B219,$B219))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="E220" s="10">
+        <f>IF($B220="","",SUMIFS($D$2:$D220,$B$2:$B220,$B220))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="E221" s="10">
+        <f>IF($B221="","",SUMIFS($D$2:$D221,$B$2:$B221,$B221))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="E222" s="10">
+        <f>IF($B222="","",SUMIFS($D$2:$D222,$B$2:$B222,$B222))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="E223" s="10">
+        <f>IF($B223="","",SUMIFS($D$2:$D223,$B$2:$B223,$B223))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="E224" s="10">
+        <f>IF($B224="","",SUMIFS($D$2:$D224,$B$2:$B224,$B224))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="E225" s="10">
+        <f>IF($B225="","",SUMIFS($D$2:$D225,$B$2:$B225,$B225))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="E226" s="10">
+        <f>IF($B226="","",SUMIFS($D$2:$D226,$B$2:$B226,$B226))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="E227" s="10">
+        <f>IF($B227="","",SUMIFS($D$2:$D227,$B$2:$B227,$B227))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="E228" s="10">
+        <f>IF($B228="","",SUMIFS($D$2:$D228,$B$2:$B228,$B228))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="E229" s="10">
+        <f>IF($B229="","",SUMIFS($D$2:$D229,$B$2:$B229,$B229))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="E230" s="10">
+        <f>IF($B230="","",SUMIFS($D$2:$D230,$B$2:$B230,$B230))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="E231" s="10">
+        <f>IF($B231="","",SUMIFS($D$2:$D231,$B$2:$B231,$B231))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="E232" s="10">
+        <f>IF($B232="","",SUMIFS($D$2:$D232,$B$2:$B232,$B232))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="E233" s="10">
+        <f>IF($B233="","",SUMIFS($D$2:$D233,$B$2:$B233,$B233))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="E234" s="10">
+        <f>IF($B234="","",SUMIFS($D$2:$D234,$B$2:$B234,$B234))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="E235" s="10">
+        <f>IF($B235="","",SUMIFS($D$2:$D235,$B$2:$B235,$B235))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="E236" s="10">
+        <f>IF($B236="","",SUMIFS($D$2:$D236,$B$2:$B236,$B236))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="E237" s="10">
+        <f>IF($B237="","",SUMIFS($D$2:$D237,$B$2:$B237,$B237))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="E238" s="10">
+        <f>IF($B238="","",SUMIFS($D$2:$D238,$B$2:$B238,$B238))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="E239" s="10">
+        <f>IF($B239="","",SUMIFS($D$2:$D239,$B$2:$B239,$B239))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="E240" s="10">
+        <f>IF($B240="","",SUMIFS($D$2:$D240,$B$2:$B240,$B240))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="E241" s="10">
+        <f>IF($B241="","",SUMIFS($D$2:$D241,$B$2:$B241,$B241))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="E242" s="10">
+        <f>IF($B242="","",SUMIFS($D$2:$D242,$B$2:$B242,$B242))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="E243" s="10">
+        <f>IF($B243="","",SUMIFS($D$2:$D243,$B$2:$B243,$B243))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="E244" s="10">
+        <f>IF($B244="","",SUMIFS($D$2:$D244,$B$2:$B244,$B244))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="E245" s="10">
+        <f>IF($B245="","",SUMIFS($D$2:$D245,$B$2:$B245,$B245))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="E246" s="10">
+        <f>IF($B246="","",SUMIFS($D$2:$D246,$B$2:$B246,$B246))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="E247" s="10">
+        <f>IF($B247="","",SUMIFS($D$2:$D247,$B$2:$B247,$B247))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="E248" s="10">
+        <f>IF($B248="","",SUMIFS($D$2:$D248,$B$2:$B248,$B248))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="E249" s="10">
+        <f>IF($B249="","",SUMIFS($D$2:$D249,$B$2:$B249,$B249))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="E250" s="10">
+        <f>IF($B250="","",SUMIFS($D$2:$D250,$B$2:$B250,$B250))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="E251" s="10">
+        <f>IF($B251="","",SUMIFS($D$2:$D251,$B$2:$B251,$B251))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="E252" s="10">
+        <f>IF($B252="","",SUMIFS($D$2:$D252,$B$2:$B252,$B252))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="E253" s="10">
+        <f>IF($B253="","",SUMIFS($D$2:$D253,$B$2:$B253,$B253))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="E254" s="10">
+        <f>IF($B254="","",SUMIFS($D$2:$D254,$B$2:$B254,$B254))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="E255" s="10">
+        <f>IF($B255="","",SUMIFS($D$2:$D255,$B$2:$B255,$B255))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="E256" s="10">
+        <f>IF($B256="","",SUMIFS($D$2:$D256,$B$2:$B256,$B256))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="E257" s="10">
+        <f>IF($B257="","",SUMIFS($D$2:$D257,$B$2:$B257,$B257))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="E258" s="10">
+        <f>IF($B258="","",SUMIFS($D$2:$D258,$B$2:$B258,$B258))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="E259" s="10">
+        <f>IF($B259="","",SUMIFS($D$2:$D259,$B$2:$B259,$B259))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="E260" s="10">
+        <f>IF($B260="","",SUMIFS($D$2:$D260,$B$2:$B260,$B260))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="E261" s="10">
+        <f>IF($B261="","",SUMIFS($D$2:$D261,$B$2:$B261,$B261))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="E262" s="10">
+        <f>IF($B262="","",SUMIFS($D$2:$D262,$B$2:$B262,$B262))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="E263" s="10">
+        <f>IF($B263="","",SUMIFS($D$2:$D263,$B$2:$B263,$B263))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="E264" s="10">
+        <f>IF($B264="","",SUMIFS($D$2:$D264,$B$2:$B264,$B264))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="E265" s="10">
+        <f>IF($B265="","",SUMIFS($D$2:$D265,$B$2:$B265,$B265))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266">
+      <c r="E266" s="10">
+        <f>IF($B266="","",SUMIFS($D$2:$D266,$B$2:$B266,$B266))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267">
+      <c r="E267" s="10">
+        <f>IF($B267="","",SUMIFS($D$2:$D267,$B$2:$B267,$B267))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="E268" s="10">
+        <f>IF($B268="","",SUMIFS($D$2:$D268,$B$2:$B268,$B268))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="E269" s="10">
+        <f>IF($B269="","",SUMIFS($D$2:$D269,$B$2:$B269,$B269))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="E270" s="10">
+        <f>IF($B270="","",SUMIFS($D$2:$D270,$B$2:$B270,$B270))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="E271" s="10">
+        <f>IF($B271="","",SUMIFS($D$2:$D271,$B$2:$B271,$B271))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="E272" s="10">
+        <f>IF($B272="","",SUMIFS($D$2:$D272,$B$2:$B272,$B272))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273">
+      <c r="E273" s="10">
+        <f>IF($B273="","",SUMIFS($D$2:$D273,$B$2:$B273,$B273))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="E274" s="10">
+        <f>IF($B274="","",SUMIFS($D$2:$D274,$B$2:$B274,$B274))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="E275" s="10">
+        <f>IF($B275="","",SUMIFS($D$2:$D275,$B$2:$B275,$B275))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="E276" s="10">
+        <f>IF($B276="","",SUMIFS($D$2:$D276,$B$2:$B276,$B276))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="E277" s="10">
+        <f>IF($B277="","",SUMIFS($D$2:$D277,$B$2:$B277,$B277))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="E278" s="10">
+        <f>IF($B278="","",SUMIFS($D$2:$D278,$B$2:$B278,$B278))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="E279" s="10">
+        <f>IF($B279="","",SUMIFS($D$2:$D279,$B$2:$B279,$B279))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="E280" s="10">
+        <f>IF($B280="","",SUMIFS($D$2:$D280,$B$2:$B280,$B280))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="E281" s="10">
+        <f>IF($B281="","",SUMIFS($D$2:$D281,$B$2:$B281,$B281))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="E282" s="10">
+        <f>IF($B282="","",SUMIFS($D$2:$D282,$B$2:$B282,$B282))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="E283" s="10">
+        <f>IF($B283="","",SUMIFS($D$2:$D283,$B$2:$B283,$B283))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="E284" s="10">
+        <f>IF($B284="","",SUMIFS($D$2:$D284,$B$2:$B284,$B284))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="E285" s="10">
+        <f>IF($B285="","",SUMIFS($D$2:$D285,$B$2:$B285,$B285))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="E286" s="10">
+        <f>IF($B286="","",SUMIFS($D$2:$D286,$B$2:$B286,$B286))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="E287" s="10">
+        <f>IF($B287="","",SUMIFS($D$2:$D287,$B$2:$B287,$B287))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="E288" s="10">
+        <f>IF($B288="","",SUMIFS($D$2:$D288,$B$2:$B288,$B288))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="E289" s="10">
+        <f>IF($B289="","",SUMIFS($D$2:$D289,$B$2:$B289,$B289))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="E290" s="10">
+        <f>IF($B290="","",SUMIFS($D$2:$D290,$B$2:$B290,$B290))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="E291" s="10">
+        <f>IF($B291="","",SUMIFS($D$2:$D291,$B$2:$B291,$B291))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="E292" s="10">
+        <f>IF($B292="","",SUMIFS($D$2:$D292,$B$2:$B292,$B292))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="E293" s="10">
+        <f>IF($B293="","",SUMIFS($D$2:$D293,$B$2:$B293,$B293))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="E294" s="10">
+        <f>IF($B294="","",SUMIFS($D$2:$D294,$B$2:$B294,$B294))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="E295" s="10">
+        <f>IF($B295="","",SUMIFS($D$2:$D295,$B$2:$B295,$B295))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="E296" s="10">
+        <f>IF($B296="","",SUMIFS($D$2:$D296,$B$2:$B296,$B296))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="E297" s="10">
+        <f>IF($B297="","",SUMIFS($D$2:$D297,$B$2:$B297,$B297))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="E298" s="10">
+        <f>IF($B298="","",SUMIFS($D$2:$D298,$B$2:$B298,$B298))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="E299" s="10">
+        <f>IF($B299="","",SUMIFS($D$2:$D299,$B$2:$B299,$B299))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="E300" s="10">
+        <f>IF($B300="","",SUMIFS($D$2:$D300,$B$2:$B300,$B300))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="E301" s="10">
+        <f>IF($B301="","",SUMIFS($D$2:$D301,$B$2:$B301,$B301))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="E302" s="10">
+        <f>IF($B302="","",SUMIFS($D$2:$D302,$B$2:$B302,$B302))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="E303" s="10">
+        <f>IF($B303="","",SUMIFS($D$2:$D303,$B$2:$B303,$B303))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="E304" s="10">
+        <f>IF($B304="","",SUMIFS($D$2:$D304,$B$2:$B304,$B304))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="E305" s="10">
+        <f>IF($B305="","",SUMIFS($D$2:$D305,$B$2:$B305,$B305))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306">
+      <c r="E306" s="10">
+        <f>IF($B306="","",SUMIFS($D$2:$D306,$B$2:$B306,$B306))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307">
+      <c r="E307" s="10">
+        <f>IF($B307="","",SUMIFS($D$2:$D307,$B$2:$B307,$B307))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308">
+      <c r="E308" s="10">
+        <f>IF($B308="","",SUMIFS($D$2:$D308,$B$2:$B308,$B308))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309">
+      <c r="E309" s="10">
+        <f>IF($B309="","",SUMIFS($D$2:$D309,$B$2:$B309,$B309))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310">
+      <c r="E310" s="10">
+        <f>IF($B310="","",SUMIFS($D$2:$D310,$B$2:$B310,$B310))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311">
+      <c r="E311" s="10">
+        <f>IF($B311="","",SUMIFS($D$2:$D311,$B$2:$B311,$B311))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312">
+      <c r="E312" s="10">
+        <f>IF($B312="","",SUMIFS($D$2:$D312,$B$2:$B312,$B312))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313">
+      <c r="E313" s="10">
+        <f>IF($B313="","",SUMIFS($D$2:$D313,$B$2:$B313,$B313))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314">
+      <c r="E314" s="10">
+        <f>IF($B314="","",SUMIFS($D$2:$D314,$B$2:$B314,$B314))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315">
+      <c r="E315" s="10">
+        <f>IF($B315="","",SUMIFS($D$2:$D315,$B$2:$B315,$B315))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316">
+      <c r="E316" s="10">
+        <f>IF($B316="","",SUMIFS($D$2:$D316,$B$2:$B316,$B316))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="E317" s="10">
+        <f>IF($B317="","",SUMIFS($D$2:$D317,$B$2:$B317,$B317))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="318">
+      <c r="E318" s="10">
+        <f>IF($B318="","",SUMIFS($D$2:$D318,$B$2:$B318,$B318))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="E319" s="10">
+        <f>IF($B319="","",SUMIFS($D$2:$D319,$B$2:$B319,$B319))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="E320" s="10">
+        <f>IF($B320="","",SUMIFS($D$2:$D320,$B$2:$B320,$B320))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="E321" s="10">
+        <f>IF($B321="","",SUMIFS($D$2:$D321,$B$2:$B321,$B321))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322">
+      <c r="E322" s="10">
+        <f>IF($B322="","",SUMIFS($D$2:$D322,$B$2:$B322,$B322))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323">
+      <c r="E323" s="10">
+        <f>IF($B323="","",SUMIFS($D$2:$D323,$B$2:$B323,$B323))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="E324" s="10">
+        <f>IF($B324="","",SUMIFS($D$2:$D324,$B$2:$B324,$B324))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="325">
+      <c r="E325" s="10">
+        <f>IF($B325="","",SUMIFS($D$2:$D325,$B$2:$B325,$B325))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="E326" s="10">
+        <f>IF($B326="","",SUMIFS($D$2:$D326,$B$2:$B326,$B326))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="E327" s="10">
+        <f>IF($B327="","",SUMIFS($D$2:$D327,$B$2:$B327,$B327))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="E328" s="10">
+        <f>IF($B328="","",SUMIFS($D$2:$D328,$B$2:$B328,$B328))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="E329" s="10">
+        <f>IF($B329="","",SUMIFS($D$2:$D329,$B$2:$B329,$B329))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="330">
+      <c r="E330" s="10">
+        <f>IF($B330="","",SUMIFS($D$2:$D330,$B$2:$B330,$B330))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331">
+      <c r="E331" s="10">
+        <f>IF($B331="","",SUMIFS($D$2:$D331,$B$2:$B331,$B331))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332">
+      <c r="E332" s="10">
+        <f>IF($B332="","",SUMIFS($D$2:$D332,$B$2:$B332,$B332))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333">
+      <c r="E333" s="10">
+        <f>IF($B333="","",SUMIFS($D$2:$D333,$B$2:$B333,$B333))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334">
+      <c r="E334" s="10">
+        <f>IF($B334="","",SUMIFS($D$2:$D334,$B$2:$B334,$B334))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335">
+      <c r="E335" s="10">
+        <f>IF($B335="","",SUMIFS($D$2:$D335,$B$2:$B335,$B335))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336">
+      <c r="E336" s="10">
+        <f>IF($B336="","",SUMIFS($D$2:$D336,$B$2:$B336,$B336))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337">
+      <c r="E337" s="10">
+        <f>IF($B337="","",SUMIFS($D$2:$D337,$B$2:$B337,$B337))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338">
+      <c r="E338" s="10">
+        <f>IF($B338="","",SUMIFS($D$2:$D338,$B$2:$B338,$B338))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339">
+      <c r="E339" s="10">
+        <f>IF($B339="","",SUMIFS($D$2:$D339,$B$2:$B339,$B339))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="E340" s="10">
+        <f>IF($B340="","",SUMIFS($D$2:$D340,$B$2:$B340,$B340))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341">
+      <c r="E341" s="10">
+        <f>IF($B341="","",SUMIFS($D$2:$D341,$B$2:$B341,$B341))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="342">
+      <c r="E342" s="10">
+        <f>IF($B342="","",SUMIFS($D$2:$D342,$B$2:$B342,$B342))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="343">
+      <c r="E343" s="10">
+        <f>IF($B343="","",SUMIFS($D$2:$D343,$B$2:$B343,$B343))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="344">
+      <c r="E344" s="10">
+        <f>IF($B344="","",SUMIFS($D$2:$D344,$B$2:$B344,$B344))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345">
+      <c r="E345" s="10">
+        <f>IF($B345="","",SUMIFS($D$2:$D345,$B$2:$B345,$B345))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346">
+      <c r="E346" s="10">
+        <f>IF($B346="","",SUMIFS($D$2:$D346,$B$2:$B346,$B346))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347">
+      <c r="E347" s="10">
+        <f>IF($B347="","",SUMIFS($D$2:$D347,$B$2:$B347,$B347))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="348">
+      <c r="E348" s="10">
+        <f>IF($B348="","",SUMIFS($D$2:$D348,$B$2:$B348,$B348))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="349">
+      <c r="E349" s="10">
+        <f>IF($B349="","",SUMIFS($D$2:$D349,$B$2:$B349,$B349))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="E350" s="10">
+        <f>IF($B350="","",SUMIFS($D$2:$D350,$B$2:$B350,$B350))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="E351" s="10">
+        <f>IF($B351="","",SUMIFS($D$2:$D351,$B$2:$B351,$B351))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="E352" s="10">
+        <f>IF($B352="","",SUMIFS($D$2:$D352,$B$2:$B352,$B352))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="E353" s="10">
+        <f>IF($B353="","",SUMIFS($D$2:$D353,$B$2:$B353,$B353))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354">
+      <c r="E354" s="10">
+        <f>IF($B354="","",SUMIFS($D$2:$D354,$B$2:$B354,$B354))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="355">
+      <c r="E355" s="10">
+        <f>IF($B355="","",SUMIFS($D$2:$D355,$B$2:$B355,$B355))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="356">
+      <c r="E356" s="10">
+        <f>IF($B356="","",SUMIFS($D$2:$D356,$B$2:$B356,$B356))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="357">
+      <c r="E357" s="10">
+        <f>IF($B357="","",SUMIFS($D$2:$D357,$B$2:$B357,$B357))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="E358" s="10">
+        <f>IF($B358="","",SUMIFS($D$2:$D358,$B$2:$B358,$B358))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="E359" s="10">
+        <f>IF($B359="","",SUMIFS($D$2:$D359,$B$2:$B359,$B359))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360">
+      <c r="E360" s="10">
+        <f>IF($B360="","",SUMIFS($D$2:$D360,$B$2:$B360,$B360))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="361">
+      <c r="E361" s="10">
+        <f>IF($B361="","",SUMIFS($D$2:$D361,$B$2:$B361,$B361))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="362">
+      <c r="E362" s="10">
+        <f>IF($B362="","",SUMIFS($D$2:$D362,$B$2:$B362,$B362))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="363">
+      <c r="E363" s="10">
+        <f>IF($B363="","",SUMIFS($D$2:$D363,$B$2:$B363,$B363))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="364">
+      <c r="E364" s="10">
+        <f>IF($B364="","",SUMIFS($D$2:$D364,$B$2:$B364,$B364))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="365">
+      <c r="E365" s="10">
+        <f>IF($B365="","",SUMIFS($D$2:$D365,$B$2:$B365,$B365))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="E366" s="10">
+        <f>IF($B366="","",SUMIFS($D$2:$D366,$B$2:$B366,$B366))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367">
+      <c r="E367" s="10">
+        <f>IF($B367="","",SUMIFS($D$2:$D367,$B$2:$B367,$B367))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="368">
+      <c r="E368" s="10">
+        <f>IF($B368="","",SUMIFS($D$2:$D368,$B$2:$B368,$B368))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="369">
+      <c r="E369" s="10">
+        <f>IF($B369="","",SUMIFS($D$2:$D369,$B$2:$B369,$B369))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="370">
+      <c r="E370" s="10">
+        <f>IF($B370="","",SUMIFS($D$2:$D370,$B$2:$B370,$B370))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="E371" s="10">
+        <f>IF($B371="","",SUMIFS($D$2:$D371,$B$2:$B371,$B371))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="E372" s="10">
+        <f>IF($B372="","",SUMIFS($D$2:$D372,$B$2:$B372,$B372))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373">
+      <c r="E373" s="10">
+        <f>IF($B373="","",SUMIFS($D$2:$D373,$B$2:$B373,$B373))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="374">
+      <c r="E374" s="10">
+        <f>IF($B374="","",SUMIFS($D$2:$D374,$B$2:$B374,$B374))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="375">
+      <c r="E375" s="10">
+        <f>IF($B375="","",SUMIFS($D$2:$D375,$B$2:$B375,$B375))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="E376" s="10">
+        <f>IF($B376="","",SUMIFS($D$2:$D376,$B$2:$B376,$B376))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="E377" s="10">
+        <f>IF($B377="","",SUMIFS($D$2:$D377,$B$2:$B377,$B377))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="E378" s="10">
+        <f>IF($B378="","",SUMIFS($D$2:$D378,$B$2:$B378,$B378))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="E379" s="10">
+        <f>IF($B379="","",SUMIFS($D$2:$D379,$B$2:$B379,$B379))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="E380" s="10">
+        <f>IF($B380="","",SUMIFS($D$2:$D380,$B$2:$B380,$B380))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="E381" s="10">
+        <f>IF($B381="","",SUMIFS($D$2:$D381,$B$2:$B381,$B381))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="E382" s="10">
+        <f>IF($B382="","",SUMIFS($D$2:$D382,$B$2:$B382,$B382))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="E383" s="10">
+        <f>IF($B383="","",SUMIFS($D$2:$D383,$B$2:$B383,$B383))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="E384" s="10">
+        <f>IF($B384="","",SUMIFS($D$2:$D384,$B$2:$B384,$B384))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="E385" s="10">
+        <f>IF($B385="","",SUMIFS($D$2:$D385,$B$2:$B385,$B385))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="E386" s="10">
+        <f>IF($B386="","",SUMIFS($D$2:$D386,$B$2:$B386,$B386))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="E387" s="10">
+        <f>IF($B387="","",SUMIFS($D$2:$D387,$B$2:$B387,$B387))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="E388" s="10">
+        <f>IF($B388="","",SUMIFS($D$2:$D388,$B$2:$B388,$B388))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="E389" s="10">
+        <f>IF($B389="","",SUMIFS($D$2:$D389,$B$2:$B389,$B389))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="390">
+      <c r="E390" s="10">
+        <f>IF($B390="","",SUMIFS($D$2:$D390,$B$2:$B390,$B390))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="391">
+      <c r="E391" s="10">
+        <f>IF($B391="","",SUMIFS($D$2:$D391,$B$2:$B391,$B391))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="E392" s="10">
+        <f>IF($B392="","",SUMIFS($D$2:$D392,$B$2:$B392,$B392))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="E393" s="10">
+        <f>IF($B393="","",SUMIFS($D$2:$D393,$B$2:$B393,$B393))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="E394" s="10">
+        <f>IF($B394="","",SUMIFS($D$2:$D394,$B$2:$B394,$B394))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="395">
+      <c r="E395" s="10">
+        <f>IF($B395="","",SUMIFS($D$2:$D395,$B$2:$B395,$B395))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="396">
+      <c r="E396" s="10">
+        <f>IF($B396="","",SUMIFS($D$2:$D396,$B$2:$B396,$B396))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="E397" s="10">
+        <f>IF($B397="","",SUMIFS($D$2:$D397,$B$2:$B397,$B397))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="E398" s="10">
+        <f>IF($B398="","",SUMIFS($D$2:$D398,$B$2:$B398,$B398))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="399">
+      <c r="E399" s="10">
+        <f>IF($B399="","",SUMIFS($D$2:$D399,$B$2:$B399,$B399))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="400">
+      <c r="E400" s="10">
+        <f>IF($B400="","",SUMIFS($D$2:$D400,$B$2:$B400,$B400))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="401">
+      <c r="E401" s="10">
+        <f>IF($B401="","",SUMIFS($D$2:$D401,$B$2:$B401,$B401))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="E402" s="10">
+        <f>IF($B402="","",SUMIFS($D$2:$D402,$B$2:$B402,$B402))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="403">
+      <c r="E403" s="10">
+        <f>IF($B403="","",SUMIFS($D$2:$D403,$B$2:$B403,$B403))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="404">
+      <c r="E404" s="10">
+        <f>IF($B404="","",SUMIFS($D$2:$D404,$B$2:$B404,$B404))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="E405" s="10">
+        <f>IF($B405="","",SUMIFS($D$2:$D405,$B$2:$B405,$B405))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406">
+      <c r="E406" s="10">
+        <f>IF($B406="","",SUMIFS($D$2:$D406,$B$2:$B406,$B406))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="E407" s="10">
+        <f>IF($B407="","",SUMIFS($D$2:$D407,$B$2:$B407,$B407))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="408">
+      <c r="E408" s="10">
+        <f>IF($B408="","",SUMIFS($D$2:$D408,$B$2:$B408,$B408))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="409">
+      <c r="E409" s="10">
+        <f>IF($B409="","",SUMIFS($D$2:$D409,$B$2:$B409,$B409))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="410">
+      <c r="E410" s="10">
+        <f>IF($B410="","",SUMIFS($D$2:$D410,$B$2:$B410,$B410))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="411">
+      <c r="E411" s="10">
+        <f>IF($B411="","",SUMIFS($D$2:$D411,$B$2:$B411,$B411))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="412">
+      <c r="E412" s="10">
+        <f>IF($B412="","",SUMIFS($D$2:$D412,$B$2:$B412,$B412))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="413">
+      <c r="E413" s="10">
+        <f>IF($B413="","",SUMIFS($D$2:$D413,$B$2:$B413,$B413))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="414">
+      <c r="E414" s="10">
+        <f>IF($B414="","",SUMIFS($D$2:$D414,$B$2:$B414,$B414))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="415">
+      <c r="E415" s="10">
+        <f>IF($B415="","",SUMIFS($D$2:$D415,$B$2:$B415,$B415))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="416">
+      <c r="E416" s="10">
+        <f>IF($B416="","",SUMIFS($D$2:$D416,$B$2:$B416,$B416))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="417">
+      <c r="E417" s="10">
+        <f>IF($B417="","",SUMIFS($D$2:$D417,$B$2:$B417,$B417))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="E418" s="10">
+        <f>IF($B418="","",SUMIFS($D$2:$D418,$B$2:$B418,$B418))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="E419" s="10">
+        <f>IF($B419="","",SUMIFS($D$2:$D419,$B$2:$B419,$B419))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="420">
+      <c r="E420" s="10">
+        <f>IF($B420="","",SUMIFS($D$2:$D420,$B$2:$B420,$B420))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="421">
+      <c r="E421" s="10">
+        <f>IF($B421="","",SUMIFS($D$2:$D421,$B$2:$B421,$B421))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="422">
+      <c r="E422" s="10">
+        <f>IF($B422="","",SUMIFS($D$2:$D422,$B$2:$B422,$B422))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="423">
+      <c r="E423" s="10">
+        <f>IF($B423="","",SUMIFS($D$2:$D423,$B$2:$B423,$B423))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="424">
+      <c r="E424" s="10">
+        <f>IF($B424="","",SUMIFS($D$2:$D424,$B$2:$B424,$B424))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="425">
+      <c r="E425" s="10">
+        <f>IF($B425="","",SUMIFS($D$2:$D425,$B$2:$B425,$B425))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="426">
+      <c r="E426" s="10">
+        <f>IF($B426="","",SUMIFS($D$2:$D426,$B$2:$B426,$B426))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="427">
+      <c r="E427" s="10">
+        <f>IF($B427="","",SUMIFS($D$2:$D427,$B$2:$B427,$B427))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="428">
+      <c r="E428" s="10">
+        <f>IF($B428="","",SUMIFS($D$2:$D428,$B$2:$B428,$B428))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="429">
+      <c r="E429" s="10">
+        <f>IF($B429="","",SUMIFS($D$2:$D429,$B$2:$B429,$B429))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="430">
+      <c r="E430" s="10">
+        <f>IF($B430="","",SUMIFS($D$2:$D430,$B$2:$B430,$B430))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="E431" s="10">
+        <f>IF($B431="","",SUMIFS($D$2:$D431,$B$2:$B431,$B431))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="432">
+      <c r="E432" s="10">
+        <f>IF($B432="","",SUMIFS($D$2:$D432,$B$2:$B432,$B432))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="433">
+      <c r="E433" s="10">
+        <f>IF($B433="","",SUMIFS($D$2:$D433,$B$2:$B433,$B433))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="434">
+      <c r="E434" s="10">
+        <f>IF($B434="","",SUMIFS($D$2:$D434,$B$2:$B434,$B434))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="435">
+      <c r="E435" s="10">
+        <f>IF($B435="","",SUMIFS($D$2:$D435,$B$2:$B435,$B435))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="436">
+      <c r="E436" s="10">
+        <f>IF($B436="","",SUMIFS($D$2:$D436,$B$2:$B436,$B436))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="437">
+      <c r="E437" s="10">
+        <f>IF($B437="","",SUMIFS($D$2:$D437,$B$2:$B437,$B437))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="438">
+      <c r="E438" s="10">
+        <f>IF($B438="","",SUMIFS($D$2:$D438,$B$2:$B438,$B438))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="439">
+      <c r="E439" s="10">
+        <f>IF($B439="","",SUMIFS($D$2:$D439,$B$2:$B439,$B439))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="440">
+      <c r="E440" s="10">
+        <f>IF($B440="","",SUMIFS($D$2:$D440,$B$2:$B440,$B440))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="E441" s="10">
+        <f>IF($B441="","",SUMIFS($D$2:$D441,$B$2:$B441,$B441))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="442">
+      <c r="E442" s="10">
+        <f>IF($B442="","",SUMIFS($D$2:$D442,$B$2:$B442,$B442))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="443">
+      <c r="E443" s="10">
+        <f>IF($B443="","",SUMIFS($D$2:$D443,$B$2:$B443,$B443))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="E444" s="10">
+        <f>IF($B444="","",SUMIFS($D$2:$D444,$B$2:$B444,$B444))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445">
+      <c r="E445" s="10">
+        <f>IF($B445="","",SUMIFS($D$2:$D445,$B$2:$B445,$B445))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="446">
+      <c r="E446" s="10">
+        <f>IF($B446="","",SUMIFS($D$2:$D446,$B$2:$B446,$B446))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="447">
+      <c r="E447" s="10">
+        <f>IF($B447="","",SUMIFS($D$2:$D447,$B$2:$B447,$B447))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="448">
+      <c r="E448" s="10">
+        <f>IF($B448="","",SUMIFS($D$2:$D448,$B$2:$B448,$B448))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="449">
+      <c r="E449" s="10">
+        <f>IF($B449="","",SUMIFS($D$2:$D449,$B$2:$B449,$B449))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="450">
+      <c r="E450" s="10">
+        <f>IF($B450="","",SUMIFS($D$2:$D450,$B$2:$B450,$B450))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="451">
+      <c r="E451" s="10">
+        <f>IF($B451="","",SUMIFS($D$2:$D451,$B$2:$B451,$B451))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="452">
+      <c r="E452" s="10">
+        <f>IF($B452="","",SUMIFS($D$2:$D452,$B$2:$B452,$B452))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="453">
+      <c r="E453" s="10">
+        <f>IF($B453="","",SUMIFS($D$2:$D453,$B$2:$B453,$B453))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="E454" s="10">
+        <f>IF($B454="","",SUMIFS($D$2:$D454,$B$2:$B454,$B454))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="455">
+      <c r="E455" s="10">
+        <f>IF($B455="","",SUMIFS($D$2:$D455,$B$2:$B455,$B455))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="456">
+      <c r="E456" s="10">
+        <f>IF($B456="","",SUMIFS($D$2:$D456,$B$2:$B456,$B456))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="E457" s="10">
+        <f>IF($B457="","",SUMIFS($D$2:$D457,$B$2:$B457,$B457))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458">
+      <c r="E458" s="10">
+        <f>IF($B458="","",SUMIFS($D$2:$D458,$B$2:$B458,$B458))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="459">
+      <c r="E459" s="10">
+        <f>IF($B459="","",SUMIFS($D$2:$D459,$B$2:$B459,$B459))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="460">
+      <c r="E460" s="10">
+        <f>IF($B460="","",SUMIFS($D$2:$D460,$B$2:$B460,$B460))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="461">
+      <c r="E461" s="10">
+        <f>IF($B461="","",SUMIFS($D$2:$D461,$B$2:$B461,$B461))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="462">
+      <c r="E462" s="10">
+        <f>IF($B462="","",SUMIFS($D$2:$D462,$B$2:$B462,$B462))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="463">
+      <c r="E463" s="10">
+        <f>IF($B463="","",SUMIFS($D$2:$D463,$B$2:$B463,$B463))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="464">
+      <c r="E464" s="10">
+        <f>IF($B464="","",SUMIFS($D$2:$D464,$B$2:$B464,$B464))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="465">
+      <c r="E465" s="10">
+        <f>IF($B465="","",SUMIFS($D$2:$D465,$B$2:$B465,$B465))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="466">
+      <c r="E466" s="10">
+        <f>IF($B466="","",SUMIFS($D$2:$D466,$B$2:$B466,$B466))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="467">
+      <c r="E467" s="10">
+        <f>IF($B467="","",SUMIFS($D$2:$D467,$B$2:$B467,$B467))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="468">
+      <c r="E468" s="10">
+        <f>IF($B468="","",SUMIFS($D$2:$D468,$B$2:$B468,$B468))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="469">
+      <c r="E469" s="10">
+        <f>IF($B469="","",SUMIFS($D$2:$D469,$B$2:$B469,$B469))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="E470" s="10">
+        <f>IF($B470="","",SUMIFS($D$2:$D470,$B$2:$B470,$B470))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="471">
+      <c r="E471" s="10">
+        <f>IF($B471="","",SUMIFS($D$2:$D471,$B$2:$B471,$B471))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="472">
+      <c r="E472" s="10">
+        <f>IF($B472="","",SUMIFS($D$2:$D472,$B$2:$B472,$B472))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="473">
+      <c r="E473" s="10">
+        <f>IF($B473="","",SUMIFS($D$2:$D473,$B$2:$B473,$B473))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="474">
+      <c r="E474" s="10">
+        <f>IF($B474="","",SUMIFS($D$2:$D474,$B$2:$B474,$B474))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="475">
+      <c r="E475" s="10">
+        <f>IF($B475="","",SUMIFS($D$2:$D475,$B$2:$B475,$B475))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="476">
+      <c r="E476" s="10">
+        <f>IF($B476="","",SUMIFS($D$2:$D476,$B$2:$B476,$B476))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="477">
+      <c r="E477" s="10">
+        <f>IF($B477="","",SUMIFS($D$2:$D477,$B$2:$B477,$B477))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="478">
+      <c r="E478" s="10">
+        <f>IF($B478="","",SUMIFS($D$2:$D478,$B$2:$B478,$B478))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="479">
+      <c r="E479" s="10">
+        <f>IF($B479="","",SUMIFS($D$2:$D479,$B$2:$B479,$B479))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="E480" s="10">
+        <f>IF($B480="","",SUMIFS($D$2:$D480,$B$2:$B480,$B480))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="481">
+      <c r="E481" s="10">
+        <f>IF($B481="","",SUMIFS($D$2:$D481,$B$2:$B481,$B481))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="482">
+      <c r="E482" s="10">
+        <f>IF($B482="","",SUMIFS($D$2:$D482,$B$2:$B482,$B482))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="E483" s="10">
+        <f>IF($B483="","",SUMIFS($D$2:$D483,$B$2:$B483,$B483))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="484">
+      <c r="E484" s="10">
+        <f>IF($B484="","",SUMIFS($D$2:$D484,$B$2:$B484,$B484))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="485">
+      <c r="E485" s="10">
+        <f>IF($B485="","",SUMIFS($D$2:$D485,$B$2:$B485,$B485))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="486">
+      <c r="E486" s="10">
+        <f>IF($B486="","",SUMIFS($D$2:$D486,$B$2:$B486,$B486))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="487">
+      <c r="E487" s="10">
+        <f>IF($B487="","",SUMIFS($D$2:$D487,$B$2:$B487,$B487))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="488">
+      <c r="E488" s="10">
+        <f>IF($B488="","",SUMIFS($D$2:$D488,$B$2:$B488,$B488))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="489">
+      <c r="E489" s="10">
+        <f>IF($B489="","",SUMIFS($D$2:$D489,$B$2:$B489,$B489))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="490">
+      <c r="E490" s="10">
+        <f>IF($B490="","",SUMIFS($D$2:$D490,$B$2:$B490,$B490))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="491">
+      <c r="E491" s="10">
+        <f>IF($B491="","",SUMIFS($D$2:$D491,$B$2:$B491,$B491))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="492">
+      <c r="E492" s="10">
+        <f>IF($B492="","",SUMIFS($D$2:$D492,$B$2:$B492,$B492))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="E493" s="10">
+        <f>IF($B493="","",SUMIFS($D$2:$D493,$B$2:$B493,$B493))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="494">
+      <c r="E494" s="10">
+        <f>IF($B494="","",SUMIFS($D$2:$D494,$B$2:$B494,$B494))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="495">
+      <c r="E495" s="10">
+        <f>IF($B495="","",SUMIFS($D$2:$D495,$B$2:$B495,$B495))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="496">
+      <c r="E496" s="10">
+        <f>IF($B496="","",SUMIFS($D$2:$D496,$B$2:$B496,$B496))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="497">
+      <c r="E497" s="10">
+        <f>IF($B497="","",SUMIFS($D$2:$D497,$B$2:$B497,$B497))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="498">
+      <c r="E498" s="10">
+        <f>IF($B498="","",SUMIFS($D$2:$D498,$B$2:$B498,$B498))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="499">
+      <c r="E499" s="10">
+        <f>IF($B499="","",SUMIFS($D$2:$D499,$B$2:$B499,$B499))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="500">
+      <c r="E500" s="10">
+        <f>IF($B500="","",SUMIFS($D$2:$D500,$B$2:$B500,$B500))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="501">
+      <c r="E501" s="10">
+        <f>IF($B501="","",SUMIFS($D$2:$D501,$B$2:$B501,$B501))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="502">
+      <c r="E502" s="10">
+        <f>IF($B502="","",SUMIFS($D$2:$D502,$B$2:$B502,$B502))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="503">
+      <c r="E503" s="10">
+        <f>IF($B503="","",SUMIFS($D$2:$D503,$B$2:$B503,$B503))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="504">
+      <c r="E504" s="10">
+        <f>IF($B504="","",SUMIFS($D$2:$D504,$B$2:$B504,$B504))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="505">
+      <c r="E505" s="10">
+        <f>IF($B505="","",SUMIFS($D$2:$D505,$B$2:$B505,$B505))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="506">
+      <c r="E506" s="10">
+        <f>IF($B506="","",SUMIFS($D$2:$D506,$B$2:$B506,$B506))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="507">
+      <c r="E507" s="10">
+        <f>IF($B507="","",SUMIFS($D$2:$D507,$B$2:$B507,$B507))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="508">
+      <c r="E508" s="10">
+        <f>IF($B508="","",SUMIFS($D$2:$D508,$B$2:$B508,$B508))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="509">
+      <c r="E509" s="10">
+        <f>IF($B509="","",SUMIFS($D$2:$D509,$B$2:$B509,$B509))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="510">
+      <c r="E510" s="10">
+        <f>IF($B510="","",SUMIFS($D$2:$D510,$B$2:$B510,$B510))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="511">
+      <c r="E511" s="10">
+        <f>IF($B511="","",SUMIFS($D$2:$D511,$B$2:$B511,$B511))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="512">
+      <c r="E512" s="10">
+        <f>IF($B512="","",SUMIFS($D$2:$D512,$B$2:$B512,$B512))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="513">
+      <c r="E513" s="10">
+        <f>IF($B513="","",SUMIFS($D$2:$D513,$B$2:$B513,$B513))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="514">
+      <c r="E514" s="10">
+        <f>IF($B514="","",SUMIFS($D$2:$D514,$B$2:$B514,$B514))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="515">
+      <c r="E515" s="10">
+        <f>IF($B515="","",SUMIFS($D$2:$D515,$B$2:$B515,$B515))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="516">
+      <c r="E516" s="10">
+        <f>IF($B516="","",SUMIFS($D$2:$D516,$B$2:$B516,$B516))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="517">
+      <c r="E517" s="10">
+        <f>IF($B517="","",SUMIFS($D$2:$D517,$B$2:$B517,$B517))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="518">
+      <c r="E518" s="10">
+        <f>IF($B518="","",SUMIFS($D$2:$D518,$B$2:$B518,$B518))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="519">
+      <c r="E519" s="10">
+        <f>IF($B519="","",SUMIFS($D$2:$D519,$B$2:$B519,$B519))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="520">
+      <c r="E520" s="10">
+        <f>IF($B520="","",SUMIFS($D$2:$D520,$B$2:$B520,$B520))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="521">
+      <c r="E521" s="10">
+        <f>IF($B521="","",SUMIFS($D$2:$D521,$B$2:$B521,$B521))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="522">
+      <c r="E522" s="10">
+        <f>IF($B522="","",SUMIFS($D$2:$D522,$B$2:$B522,$B522))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="523">
+      <c r="E523" s="10">
+        <f>IF($B523="","",SUMIFS($D$2:$D523,$B$2:$B523,$B523))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="524">
+      <c r="E524" s="10">
+        <f>IF($B524="","",SUMIFS($D$2:$D524,$B$2:$B524,$B524))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="525">
+      <c r="E525" s="10">
+        <f>IF($B525="","",SUMIFS($D$2:$D525,$B$2:$B525,$B525))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="526">
+      <c r="E526" s="10">
+        <f>IF($B526="","",SUMIFS($D$2:$D526,$B$2:$B526,$B526))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="527">
+      <c r="E527" s="10">
+        <f>IF($B527="","",SUMIFS($D$2:$D527,$B$2:$B527,$B527))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="528">
+      <c r="E528" s="10">
+        <f>IF($B528="","",SUMIFS($D$2:$D528,$B$2:$B528,$B528))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="529">
+      <c r="E529" s="10">
+        <f>IF($B529="","",SUMIFS($D$2:$D529,$B$2:$B529,$B529))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="530">
+      <c r="E530" s="10">
+        <f>IF($B530="","",SUMIFS($D$2:$D530,$B$2:$B530,$B530))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="531">
+      <c r="E531" s="10">
+        <f>IF($B531="","",SUMIFS($D$2:$D531,$B$2:$B531,$B531))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="532">
+      <c r="E532" s="10">
+        <f>IF($B532="","",SUMIFS($D$2:$D532,$B$2:$B532,$B532))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="533">
+      <c r="E533" s="10">
+        <f>IF($B533="","",SUMIFS($D$2:$D533,$B$2:$B533,$B533))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="534">
+      <c r="E534" s="10">
+        <f>IF($B534="","",SUMIFS($D$2:$D534,$B$2:$B534,$B534))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="535">
+      <c r="E535" s="10">
+        <f>IF($B535="","",SUMIFS($D$2:$D535,$B$2:$B535,$B535))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="536">
+      <c r="E536" s="10">
+        <f>IF($B536="","",SUMIFS($D$2:$D536,$B$2:$B536,$B536))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="537">
+      <c r="E537" s="10">
+        <f>IF($B537="","",SUMIFS($D$2:$D537,$B$2:$B537,$B537))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="538">
+      <c r="E538" s="10">
+        <f>IF($B538="","",SUMIFS($D$2:$D538,$B$2:$B538,$B538))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="539">
+      <c r="E539" s="10">
+        <f>IF($B539="","",SUMIFS($D$2:$D539,$B$2:$B539,$B539))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="540">
+      <c r="E540" s="10">
+        <f>IF($B540="","",SUMIFS($D$2:$D540,$B$2:$B540,$B540))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="541">
+      <c r="E541" s="10">
+        <f>IF($B541="","",SUMIFS($D$2:$D541,$B$2:$B541,$B541))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="542">
+      <c r="E542" s="10">
+        <f>IF($B542="","",SUMIFS($D$2:$D542,$B$2:$B542,$B542))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="543">
+      <c r="E543" s="10">
+        <f>IF($B543="","",SUMIFS($D$2:$D543,$B$2:$B543,$B543))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="544">
+      <c r="E544" s="10">
+        <f>IF($B544="","",SUMIFS($D$2:$D544,$B$2:$B544,$B544))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="545">
+      <c r="E545" s="10">
+        <f>IF($B545="","",SUMIFS($D$2:$D545,$B$2:$B545,$B545))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="546">
+      <c r="E546" s="10">
+        <f>IF($B546="","",SUMIFS($D$2:$D546,$B$2:$B546,$B546))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="547">
+      <c r="E547" s="10">
+        <f>IF($B547="","",SUMIFS($D$2:$D547,$B$2:$B547,$B547))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="548">
+      <c r="E548" s="10">
+        <f>IF($B548="","",SUMIFS($D$2:$D548,$B$2:$B548,$B548))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="549">
+      <c r="E549" s="10">
+        <f>IF($B549="","",SUMIFS($D$2:$D549,$B$2:$B549,$B549))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="550">
+      <c r="E550" s="10">
+        <f>IF($B550="","",SUMIFS($D$2:$D550,$B$2:$B550,$B550))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="551">
+      <c r="E551" s="10">
+        <f>IF($B551="","",SUMIFS($D$2:$D551,$B$2:$B551,$B551))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="552">
+      <c r="E552" s="10">
+        <f>IF($B552="","",SUMIFS($D$2:$D552,$B$2:$B552,$B552))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="553">
+      <c r="E553" s="10">
+        <f>IF($B553="","",SUMIFS($D$2:$D553,$B$2:$B553,$B553))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="554">
+      <c r="E554" s="10">
+        <f>IF($B554="","",SUMIFS($D$2:$D554,$B$2:$B554,$B554))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="555">
+      <c r="E555" s="10">
+        <f>IF($B555="","",SUMIFS($D$2:$D555,$B$2:$B555,$B555))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="556">
+      <c r="E556" s="10">
+        <f>IF($B556="","",SUMIFS($D$2:$D556,$B$2:$B556,$B556))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="557">
+      <c r="E557" s="10">
+        <f>IF($B557="","",SUMIFS($D$2:$D557,$B$2:$B557,$B557))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="558">
+      <c r="E558" s="10">
+        <f>IF($B558="","",SUMIFS($D$2:$D558,$B$2:$B558,$B558))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="559">
+      <c r="E559" s="10">
+        <f>IF($B559="","",SUMIFS($D$2:$D559,$B$2:$B559,$B559))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="560">
+      <c r="E560" s="10">
+        <f>IF($B560="","",SUMIFS($D$2:$D560,$B$2:$B560,$B560))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="561">
+      <c r="E561" s="10">
+        <f>IF($B561="","",SUMIFS($D$2:$D561,$B$2:$B561,$B561))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="562">
+      <c r="E562" s="10">
+        <f>IF($B562="","",SUMIFS($D$2:$D562,$B$2:$B562,$B562))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="563">
+      <c r="E563" s="10">
+        <f>IF($B563="","",SUMIFS($D$2:$D563,$B$2:$B563,$B563))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="564">
+      <c r="E564" s="10">
+        <f>IF($B564="","",SUMIFS($D$2:$D564,$B$2:$B564,$B564))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="565">
+      <c r="E565" s="10">
+        <f>IF($B565="","",SUMIFS($D$2:$D565,$B$2:$B565,$B565))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="566">
+      <c r="E566" s="10">
+        <f>IF($B566="","",SUMIFS($D$2:$D566,$B$2:$B566,$B566))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="567">
+      <c r="E567" s="10">
+        <f>IF($B567="","",SUMIFS($D$2:$D567,$B$2:$B567,$B567))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="568">
+      <c r="E568" s="10">
+        <f>IF($B568="","",SUMIFS($D$2:$D568,$B$2:$B568,$B568))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="569">
+      <c r="E569" s="10">
+        <f>IF($B569="","",SUMIFS($D$2:$D569,$B$2:$B569,$B569))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="570">
+      <c r="E570" s="10">
+        <f>IF($B570="","",SUMIFS($D$2:$D570,$B$2:$B570,$B570))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="571">
+      <c r="E571" s="10">
+        <f>IF($B571="","",SUMIFS($D$2:$D571,$B$2:$B571,$B571))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="572">
+      <c r="E572" s="10">
+        <f>IF($B572="","",SUMIFS($D$2:$D572,$B$2:$B572,$B572))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="573">
+      <c r="E573" s="10">
+        <f>IF($B573="","",SUMIFS($D$2:$D573,$B$2:$B573,$B573))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="574">
+      <c r="E574" s="10">
+        <f>IF($B574="","",SUMIFS($D$2:$D574,$B$2:$B574,$B574))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="575">
+      <c r="E575" s="10">
+        <f>IF($B575="","",SUMIFS($D$2:$D575,$B$2:$B575,$B575))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="576">
+      <c r="E576" s="10">
+        <f>IF($B576="","",SUMIFS($D$2:$D576,$B$2:$B576,$B576))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="577">
+      <c r="E577" s="10">
+        <f>IF($B577="","",SUMIFS($D$2:$D577,$B$2:$B577,$B577))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="578">
+      <c r="E578" s="10">
+        <f>IF($B578="","",SUMIFS($D$2:$D578,$B$2:$B578,$B578))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="579">
+      <c r="E579" s="10">
+        <f>IF($B579="","",SUMIFS($D$2:$D579,$B$2:$B579,$B579))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="580">
+      <c r="E580" s="10">
+        <f>IF($B580="","",SUMIFS($D$2:$D580,$B$2:$B580,$B580))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="581">
+      <c r="E581" s="10">
+        <f>IF($B581="","",SUMIFS($D$2:$D581,$B$2:$B581,$B581))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="582">
+      <c r="E582" s="10">
+        <f>IF($B582="","",SUMIFS($D$2:$D582,$B$2:$B582,$B582))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="583">
+      <c r="E583" s="10">
+        <f>IF($B583="","",SUMIFS($D$2:$D583,$B$2:$B583,$B583))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="584">
+      <c r="E584" s="10">
+        <f>IF($B584="","",SUMIFS($D$2:$D584,$B$2:$B584,$B584))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="585">
+      <c r="E585" s="10">
+        <f>IF($B585="","",SUMIFS($D$2:$D585,$B$2:$B585,$B585))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="586">
+      <c r="E586" s="10">
+        <f>IF($B586="","",SUMIFS($D$2:$D586,$B$2:$B586,$B586))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="587">
+      <c r="E587" s="10">
+        <f>IF($B587="","",SUMIFS($D$2:$D587,$B$2:$B587,$B587))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="588">
+      <c r="E588" s="10">
+        <f>IF($B588="","",SUMIFS($D$2:$D588,$B$2:$B588,$B588))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="589">
+      <c r="E589" s="10">
+        <f>IF($B589="","",SUMIFS($D$2:$D589,$B$2:$B589,$B589))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="590">
+      <c r="E590" s="10">
+        <f>IF($B590="","",SUMIFS($D$2:$D590,$B$2:$B590,$B590))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="591">
+      <c r="E591" s="10">
+        <f>IF($B591="","",SUMIFS($D$2:$D591,$B$2:$B591,$B591))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="592">
+      <c r="E592" s="10">
+        <f>IF($B592="","",SUMIFS($D$2:$D592,$B$2:$B592,$B592))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="593">
+      <c r="E593" s="10">
+        <f>IF($B593="","",SUMIFS($D$2:$D593,$B$2:$B593,$B593))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="594">
+      <c r="E594" s="10">
+        <f>IF($B594="","",SUMIFS($D$2:$D594,$B$2:$B594,$B594))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="595">
+      <c r="E595" s="10">
+        <f>IF($B595="","",SUMIFS($D$2:$D595,$B$2:$B595,$B595))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="596">
+      <c r="E596" s="10">
+        <f>IF($B596="","",SUMIFS($D$2:$D596,$B$2:$B596,$B596))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="597">
+      <c r="E597" s="10">
+        <f>IF($B597="","",SUMIFS($D$2:$D597,$B$2:$B597,$B597))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="598">
+      <c r="E598" s="10">
+        <f>IF($B598="","",SUMIFS($D$2:$D598,$B$2:$B598,$B598))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="599">
+      <c r="E599" s="10">
+        <f>IF($B599="","",SUMIFS($D$2:$D599,$B$2:$B599,$B599))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="600">
+      <c r="E600" s="10">
+        <f>IF($B600="","",SUMIFS($D$2:$D600,$B$2:$B600,$B600))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G600"/>
   <dataValidations count="1">
     <dataValidation sqref="C2:C600" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Lists!$I$2:$I$6</formula1>
+      <formula1>Lists!$I$2:$I$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4697,151 +8318,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B24"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>TRESOR COUTURE — MASTER CATALOGUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="13" t="inlineStr"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>ONE ROW = ONE SELLABLE SKU. Each colourway is its own row because it is separately purchasable stock (this mirrors the website database: the Product ID column is the site id, so the two always reconcile).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="13" t="inlineStr"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>SHEETS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Catalogue — the single unified sheet: identity, category, pricing, tax, stock, photo and listing state per SKU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Stock Log — every stock movement, one row per event: Opening / Received / Sold / Returned / Adjustment. This answers "when did the stock come" permanently — never edit old rows, only add new ones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Lists — the dropdown sources. Add a supplier or category here and every dropdown picks it up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>HOW STOCK RECONCILES</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>"Stock per Log" sums the Stock Log for that Product ID. "Log Match" turns red (CHECK) whenever the log and the Stock Qty column disagree — that is how you catch untracked movements. Keep Stock Qty as the live truth and record every change in the log, and the two stay green.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="13" t="inlineStr"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>CELL COLOURS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Blue text = a number you typed (e.g. Buying Price). Black = calculated, do not overwrite (Margin %, Stock Status, Stock per Log, Log Match).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Red fill = OUT OF STOCK or a log mismatch. Amber fill = at/below reorder level.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>ASSUMPTIONS IN THE SAMPLE FILE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Buying prices are ILLUSTRATIVE (≈58–62% of selling price) — the database does not store cost prices yet. Replace them with real purchase-order costs. Source: generated from the live site database on 2026-08-16.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>GST Rate defaults to 5% and HSN is left blank pending your CA's confirmation. Note: garments above ₹2,500 per piece attract 18% under the Sept-2025 rate structure — confirm before relying on the 5% default.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>The Stock Log sample month (9 Jul – 16 Aug 2026) uses real products and current stock levels; the individual sale/return events are illustrative examples in the correct format.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>PHOTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>The Photo column holds a thumbnail (sample file) and Image URL holds the live site image. For new products, paste the image URL; add the thumbnail with Insert → Picture → Place in Cell if you want it inline.</t>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Order Date</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Order No.</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>City / Country</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>Order Value (₹)</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>Fulfilment</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>Return Status</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>Refund (₹)</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t>Refund Date</t>
+        </is>
+      </c>
+      <c r="N1" s="11" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ORD-0001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Website - COD</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE — delete</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>lc-example-1</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1299</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>COD - to collect</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Placed</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="7" t="n"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>EXAMPLE ROW — one row per order; fill Return/Refund columns only if a return happens</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N400"/>
+  <dataValidations count="4">
+    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$K$2:$K$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$L$2:$L$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$M$2:$M$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$N$2:$N$8</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4852,7 +8491,887 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Done Date</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Rotate the Firebase service-account key (Firebase Console → Project settings → Service accounts → generate new, delete old)</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="n"/>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Current key was shared in chat — treat as exposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Regenerate the live Razorpay Key Secret; update RAZORPAY_KEY_SECRET in Vercel</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Old secret appeared in a screenshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Paste VITE_GSTIN (from the GST certificate) into Vercel and redeploy</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Until then invoices/footer omit the GSTIN by design</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Update VITE_BUSINESS_ADDRESS in Vercel to the full registered address (Gachibowli · 500046)</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Must match the GST certificate on invoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Add CRON_SECRET + GOOGLE_REVIEW_URL in Vercel to switch on the review-request emails</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Cron is deployed and waiting on these two values</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Create the free Microsoft Clarity project; paste VITE_CLARITY_PROJECT_ID into Vercel; redeploy</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Heatmaps + session recordings, consent-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Connect Google Search Console (Domain property, DNS TXT) and submit sitemap.xml</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>62 real URLs are live and waiting to be indexed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Request indexing for home, Lehenga Cholis category, and 2–3 product pages (URL Inspection)</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>After Search Console verifies</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Google Business Profile: rewrite description (boutique, not fabric house), add secondary categories, In-store shopping, full address + PIN</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Draft description was provided in chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Google Business Profile: upload logo, cover photo, 15–25 real photos; set hours; add Products</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Profile strength currently 64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Collect the first 15–25 Google reviews (ask at handover + review-request email)</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Zero reviews today — the #1 local ranking factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>CA: confirm GST rates (5% vs 18% over ₹2,500/piece) and HSN codes per category</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Then per-product rates get wired into checkout + invoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Replace illustrative buying prices in this workbook with real PO costs</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Blue cells on the Catalogue sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Reshoot 3 product photos: HA6378, MI263, RI5687 (warehouse snapshots today)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Flagged in Photo Quality column</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>One live low-value Razorpay test payment after the key rotation</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Proves the full prepaid path end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Open Google Ads account with the new-advertiser spend-match credit (Search only)</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Do AFTER reviews exist + GA4 conversions imported</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Set SENTRY_DSN in Vercel for server error alerting</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Hooks are wired on all 12 API functions, currently inert</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>If exporting: IEC registration + LUT filing (zero-rated exports without paying IGST)</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Only when international orders start</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G120"/>
+  <conditionalFormatting sqref="D2:D120">
+    <cfRule type="expression" priority="1" dxfId="2">
+      <formula>$D2="Done"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$D2="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>$D2="Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$O$2:$O$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D120" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$P$2:$P$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:B37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="15" customHeight="1">
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>TRESOR COUTURE — MASTER CATALOGUE (read this page first)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="B3" s="16" t="inlineStr"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>WHAT EACH SHEET IS FOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Catalogue = your products. One row per item you sell. This is where prices, stock and photos live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Stock Log = a diary of stock. Every time stock moves — in or out — you add ONE line at the bottom. You never edit old lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Orders &amp; Returns = your orders. One row per customer order. Refunds and return progress are tracked HERE, because a refund is about money, not stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Action Tracker = your to-do list. Filter the Status column to "Pending" to see everything left to do; set it to "Done" with a date when finished.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Lists = the options inside every dropdown. Add a new supplier or category here once and every dropdown learns it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="B10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>THE STOCK LOG, EXPLAINED SIMPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Think of it as a bank passbook, but for stock instead of money. Stock coming in = deposit (+). Stock going out = withdrawal (−). The "Stock After" column is the balance after each line — watch it go 5 → 4 → 5 for a lehenga that was sold and then returned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>You only ever ADD a line at the bottom. The Catalogue compares this diary against the Stock Qty column and shows a red CHECK if they ever disagree — that is how you catch a movement nobody wrote down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="B14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>WHICH LINE DO I ADD WHEN… (every scenario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>New stock arrives from a supplier  →  "Received (new stock)", qty +N, reference = PO number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Someone buys on the website  →  "Sold - Online", qty −1, reference = order number. Also add the order on the Orders &amp; Returns sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Someone buys at the studio  →  "Sold - In Store", qty −1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>An export / international order ships  →  "Sold - Export", qty −1. (GST is zero-rated on exports — flag it to your CA.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>A customer returns an item and it is resellable  →  "Returned (back to stock)", qty +1. The REFUND goes on the Orders &amp; Returns sheet, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>A customer returns an item and it is damaged  →  add NOTHING here (stock is not coming back); record the refund on Orders &amp; Returns; optionally "Damaged / Write-off" if it was restocked first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>An item is damaged / lost in the studio  →  "Damaged / Write-off", qty −1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>You gift a piece or send a sample  →  "Sample / Gift", qty −1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>A physical count finds the sheet is wrong  →  "Count correction", qty +/− the difference, note why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="B25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>REFUNDS IN ONE SENTENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Money out = Orders &amp; Returns sheet (Refund column). Item back on the shelf = one "+1 Returned" line in the Stock Log. A refund with no restockable item touches ONLY the Orders sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="B28" s="16" t="inlineStr"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>HOW TO FILTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Every sheet already has filter arrows in row 1. Examples: Action Tracker → Status arrow → tick "Pending" = everything still to do. Stock Log → Product ID arrow → one product = that product's full history. Orders &amp; Returns → Return Status arrow = all open returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="B31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>CELL COLOURS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Blue text = numbers you typed (e.g. Buying Price). Black = calculated for you — do not overwrite (Margin %, Stock Status, Stock After, Log Match).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Red fill = out of stock, or the log disagrees with the stock column. Amber = at/below reorder level, or a Pending task. Green = a Done task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="16" t="inlineStr"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>ASSUMPTIONS IN THE SAMPLE FILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Buying prices are ILLUSTRATIVE (the website database stores no cost prices yet) — replace with real PO costs. GST is left at 5% with HSN blank pending your CA; garments above ₹2,500/piece likely attract 18%. The orders and stock movements are format examples using your real products and current stock levels. Generated from the live site database on 2026-08-16.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4865,6 +9384,12 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4918,6 +9443,36 @@
           <t>Supplier</t>
         </is>
       </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t>Fulfilment</t>
+        </is>
+      </c>
+      <c r="N1" s="11" t="inlineStr">
+        <is>
+          <t>Return Status</t>
+        </is>
+      </c>
+      <c r="O1" s="11" t="inlineStr">
+        <is>
+          <t>Task Area</t>
+        </is>
+      </c>
+      <c r="P1" s="11" t="inlineStr">
+        <is>
+          <t>Task Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -4935,7 +9490,7 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="17" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -4960,12 +9515,42 @@
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>Opening</t>
+          <t>Opening stock</t>
         </is>
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
           <t>Supplier A (rename me)</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>Website - COD</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>COD - to collect</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>Placed</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -4985,7 +9570,7 @@
           <t>per meter</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="17" t="n">
         <v>0.05</v>
       </c>
       <c r="E3" s="10" t="inlineStr">
@@ -5010,12 +9595,42 @@
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Received (new stock)</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
           <t>Supplier B (rename me)</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Website - Prepaid</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>COD - collected</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Packed</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -5035,7 +9650,7 @@
           <t>bundle</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="17" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -5055,12 +9670,42 @@
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>Sold</t>
+          <t>Sold - Online</t>
         </is>
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Atelier — own production</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>In Store</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Prepaid - paid</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>Pickup arranged</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -5075,7 +9720,7 @@
           <t>Wool</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="17" t="n">
         <v>0.18</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -5085,7 +9730,37 @@
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Sold - In Store</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>WhatsApp / DM</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Refunded</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>Received back</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5102,7 +9777,32 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>Adjustment</t>
+          <t>Sold - Export</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Partly refunded</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>Refunded</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>Catalogue</t>
         </is>
       </c>
     </row>
@@ -5117,6 +9817,21 @@
           <t>Satin</t>
         </is>
       </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Returned (back to stock)</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>Replaced</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -5129,6 +9844,21 @@
           <t>Net</t>
         </is>
       </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Damaged / Write-off</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -5141,11 +9871,21 @@
           <t>Georgette</t>
         </is>
       </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Sample / Gift</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Organza</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Count correction</t>
         </is>
       </c>
     </row>

--- a/docs/ops/tresor-catalogue-TEMPLATE.xlsx
+++ b/docs/ops/tresor-catalogue-TEMPLATE.xlsx
@@ -4607,7 +4607,7 @@
   </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the Master Category dropdown (or edit the Lists sheet to add one)." type="list">
-      <formula1>Lists!$A$2:$A$9</formula1>
+      <formula1>Lists!$A$2:$A$16</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the Material dropdown (or edit the Lists sheet to add one)." type="list">
       <formula1>Lists!$B$2:$B$11</formula1>
@@ -9445,11 +9445,6 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Master Category</t>
-        </is>
-      </c>
       <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Material</t>
@@ -9819,7 +9814,7 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Lehenga Cholis</t>
+          <t>One Minute Saree</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -9861,7 +9856,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Anarkalis</t>
+          <t>Half Saree</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -9888,7 +9883,7 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Western Wear</t>
+          <t>Lehenga Cholis</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -9915,36 +9910,81 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
+          <t>Langha Jacket</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Georgette</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>Sample / Gift</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Anarkalis</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Organza</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>Count correction</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Gown</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Three Piece Set</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Ethnic Wear</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Masakhali</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Western Wear</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
           <t>Studios Prêt</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Georgette</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>Sample / Gift</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Organza</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>Count correction</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Mixed</t>
         </is>
       </c>
     </row>
